--- a/artfynd/A 43963-2023 artfynd.xlsx
+++ b/artfynd/A 43963-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43963-2023 artfynd.xlsx
+++ b/artfynd/A 43963-2023 artfynd.xlsx
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119752401</v>
+        <v>119747749</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1210,13 +1210,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1227,10 +1231,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610822</v>
+        <v>610849</v>
       </c>
       <c r="R6" t="n">
-        <v>6959347</v>
+        <v>6959381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1271,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Liten hänsynsyta nära kant, I Västra delen.</t>
+          <t>3 blomställningar, ca 15 rosetter. I SÖ kanten av liten hänsynsyta, 30 m i diam.  Avverkat dec 2023.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,6 +1283,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,7 +1304,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119747749</v>
+        <v>119752401</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1330,17 +1339,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610849</v>
+        <v>610822</v>
       </c>
       <c r="R7" t="n">
-        <v>6959381</v>
+        <v>6959347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,7 +1396,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 blomställningar, ca 15 rosetter. I SÖ kanten av liten hänsynsyta, 30 m i diam.  Avverkat dec 2023.</t>
+          <t>Liten hänsynsyta nära kant, I Västra delen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,11 +1408,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 43963-2023 artfynd.xlsx
+++ b/artfynd/A 43963-2023 artfynd.xlsx
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119747749</v>
+        <v>119752401</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1210,17 +1210,13 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1231,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610849</v>
+        <v>610822</v>
       </c>
       <c r="R6" t="n">
-        <v>6959381</v>
+        <v>6959347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,7 +1267,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3 blomställningar, ca 15 rosetter. I SÖ kanten av liten hänsynsyta, 30 m i diam.  Avverkat dec 2023.</t>
+          <t>Liten hänsynsyta nära kant, I Västra delen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,11 +1279,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1304,7 +1295,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119752401</v>
+        <v>119747749</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1339,13 +1330,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610822</v>
+        <v>610849</v>
       </c>
       <c r="R7" t="n">
-        <v>6959347</v>
+        <v>6959381</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,7 +1391,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Liten hänsynsyta nära kant, I Västra delen.</t>
+          <t>3 blomställningar, ca 15 rosetter. I SÖ kanten av liten hänsynsyta, 30 m i diam.  Avverkat dec 2023.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,6 +1403,11 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 43963-2023 artfynd.xlsx
+++ b/artfynd/A 43963-2023 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119752401</v>
+        <v>119747749</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,13 +1210,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1227,10 +1231,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610822</v>
+        <v>610849</v>
       </c>
       <c r="R6" t="n">
-        <v>6959347</v>
+        <v>6959381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1271,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Liten hänsynsyta nära kant, I Västra delen.</t>
+          <t>3 blomställningar, ca 15 rosetter. I SÖ kanten av liten hänsynsyta, 30 m i diam.  Avverkat dec 2023.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,6 +1283,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,10 +1304,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119747749</v>
+        <v>119752401</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,17 +1339,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610849</v>
+        <v>610822</v>
       </c>
       <c r="R7" t="n">
-        <v>6959381</v>
+        <v>6959347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,7 +1396,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3 blomställningar, ca 15 rosetter. I SÖ kanten av liten hänsynsyta, 30 m i diam.  Avverkat dec 2023.</t>
+          <t>Liten hänsynsyta nära kant, I Västra delen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,11 +1408,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
